--- a/admin/Plantilla_Contenido_Mision_Admision_v0.8.0.xlsx
+++ b/admin/Plantilla_Contenido_Mision_Admision_v0.8.0.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" r:id="R44e1d387be2149af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="2" r:id="R9037fea0467f4e38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preguntas" sheetId="3" r:id="Rfa8a26de6e8a4450"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retos" sheetId="4" r:id="R7bbf6dc17eeb4dd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cards" sheetId="5" r:id="R3dc04365476d440c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rangos" sheetId="6" r:id="Re4a226fbc5cc47a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="7" r:id="R91f526270ffe48dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" r:id="R5743ad3f00ea464e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="2" r:id="R8dba1229320d4fbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preguntas" sheetId="3" r:id="R058110104142466d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retos" sheetId="4" r:id="R94a1e076e60f4a47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cards" sheetId="5" r:id="Rb3bcd696435741e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rangos" sheetId="6" r:id="Rd831f068b0e8405f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="7" r:id="Re01507d5c85d4dd6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -42,7 +42,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -69,123 +69,38 @@
         <x:fgColor rgb="FFFFF8E1"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF3559B7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="20">
     <x:border/>
     <x:border/>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="68">
+  <x:cellXfs count="79">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -333,6 +248,33 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -577,7 +519,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>Misión Admisión — Plantilla de contenido v0.8.0</x:v>
+        <x:v>Misión Admisión — Plantilla de contenido v0.10.7</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -694,7 +636,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B9" s="35" t="str">
-        <x:v>Las URLs deben comenzar con https://.</x:v>
+        <x:v>Las imágenes de preguntas e incisos deben usar URL HTTPS. Cada inciso puede tener texto, imagen o ambos.</x:v>
       </x:c>
       <x:c r="D9" t="str"/>
       <x:c r="E9" t="str"/>
@@ -916,775 +858,871 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="52" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="46" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="23" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="23" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="23" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="23" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="32" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="30" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="30" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="22" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="28" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="12" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="12" t="str">
+      <x:c r="A1" s="72" t="str">
         <x:v>id</x:v>
       </x:c>
-      <x:c r="B1" s="12" t="str">
+      <x:c r="B1" s="72" t="str">
         <x:v>enunciado</x:v>
       </x:c>
-      <x:c r="C1" s="12" t="str">
+      <x:c r="C1" s="72" t="str">
         <x:v>imagen_url</x:v>
       </x:c>
-      <x:c r="D1" s="12" t="str">
+      <x:c r="D1" s="72" t="str">
         <x:v>opcion_a</x:v>
       </x:c>
-      <x:c r="E1" s="12" t="str">
+      <x:c r="E1" s="72" t="str">
+        <x:v>imagen_opcion_a</x:v>
+      </x:c>
+      <x:c r="F1" s="72" t="str">
         <x:v>opcion_b</x:v>
       </x:c>
-      <x:c r="F1" s="12" t="str">
+      <x:c r="G1" s="72" t="str">
+        <x:v>imagen_opcion_b</x:v>
+      </x:c>
+      <x:c r="H1" s="72" t="str">
         <x:v>opcion_c</x:v>
       </x:c>
-      <x:c r="G1" s="12" t="str">
+      <x:c r="I1" s="72" t="str">
+        <x:v>imagen_opcion_c</x:v>
+      </x:c>
+      <x:c r="J1" s="72" t="str">
         <x:v>opcion_d</x:v>
       </x:c>
-      <x:c r="H1" s="12" t="str">
+      <x:c r="K1" s="72" t="str">
+        <x:v>imagen_opcion_d</x:v>
+      </x:c>
+      <x:c r="L1" s="72" t="str">
         <x:v>respuesta_correcta</x:v>
       </x:c>
-      <x:c r="I1" s="12" t="str">
+      <x:c r="M1" s="72" t="str">
         <x:v>categoria</x:v>
       </x:c>
-      <x:c r="J1" s="12" t="str">
+      <x:c r="N1" s="72" t="str">
         <x:v>etiquetas</x:v>
       </x:c>
-      <x:c r="K1" s="12" t="str">
+      <x:c r="O1" s="72" t="str">
         <x:v>dificultad</x:v>
       </x:c>
-      <x:c r="L1" s="12" t="str">
+      <x:c r="P1" s="72" t="str">
         <x:v>activa</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="64" t="str">
+    <x:row r="2" ht="32" customHeight="1">
+      <x:c r="A2" s="77" t="str">
         <x:v>MAT-ARI-001</x:v>
       </x:c>
-      <x:c r="B2" s="66" t="str">
+      <x:c r="B2" s="77" t="str">
         <x:v>¿Cuál es el resultado de 18 + 27?</x:v>
       </x:c>
-      <x:c r="C2" s="66" t="str"/>
-      <x:c r="D2" s="66" t="str">
+      <x:c r="C2" s="77"/>
+      <x:c r="D2" s="77" t="str">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="E2" s="66" t="str">
+      <x:c r="E2" s="77"/>
+      <x:c r="F2" s="77" t="str">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="F2" s="66" t="str">
+      <x:c r="G2" s="77"/>
+      <x:c r="H2" s="77" t="str">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G2" s="66" t="str">
+      <x:c r="I2" s="77"/>
+      <x:c r="J2" s="77" t="str">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="H2" s="64" t="str">
+      <x:c r="K2" s="77"/>
+      <x:c r="L2" s="77" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="I2" s="64" t="str">
+      <x:c r="M2" s="78" t="str">
         <x:v>matematicas</x:v>
       </x:c>
-      <x:c r="J2" s="66" t="str">
+      <x:c r="N2" s="78" t="str">
         <x:v>aritmetica;suma</x:v>
       </x:c>
-      <x:c r="K2" s="64" t="str">
+      <x:c r="O2" s="78" t="str">
         <x:v>basico</x:v>
       </x:c>
-      <x:c r="L2" s="64" t="str">
+      <x:c r="P2" s="78" t="str">
         <x:v>SI</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="64" t="str">
+    <x:row r="3" ht="32" customHeight="1">
+      <x:c r="A3" s="77" t="str">
         <x:v>MAT-ARI-002</x:v>
       </x:c>
-      <x:c r="B3" s="66" t="str">
+      <x:c r="B3" s="77" t="str">
         <x:v>¿Cuál es el resultado de 72 ÷ 8?</x:v>
       </x:c>
-      <x:c r="C3" s="66" t="str"/>
-      <x:c r="D3" s="66" t="str">
+      <x:c r="C3" s="77"/>
+      <x:c r="D3" s="77" t="str">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E3" s="66" t="str">
+      <x:c r="E3" s="77"/>
+      <x:c r="F3" s="77" t="str">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F3" s="66" t="str">
+      <x:c r="G3" s="77"/>
+      <x:c r="H3" s="77" t="str">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G3" s="66" t="str">
+      <x:c r="I3" s="77"/>
+      <x:c r="J3" s="77" t="str">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H3" s="64" t="str">
+      <x:c r="K3" s="77"/>
+      <x:c r="L3" s="77" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="I3" s="64" t="str">
+      <x:c r="M3" s="78" t="str">
         <x:v>matematicas</x:v>
       </x:c>
-      <x:c r="J3" s="66" t="str">
+      <x:c r="N3" s="78" t="str">
         <x:v>aritmetica;division</x:v>
       </x:c>
-      <x:c r="K3" s="64" t="str">
+      <x:c r="O3" s="78" t="str">
         <x:v>basico</x:v>
       </x:c>
-      <x:c r="L3" s="64" t="str">
+      <x:c r="P3" s="78" t="str">
         <x:v>SI</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="64" t="str">
+    <x:row r="4" ht="32" customHeight="1">
+      <x:c r="A4" s="77" t="str">
         <x:v>MAT-ALG-001</x:v>
       </x:c>
-      <x:c r="B4" s="66" t="str">
+      <x:c r="B4" s="77" t="str">
         <x:v>Si 3x + 5 = 20, ¿cuál es el valor de x?</x:v>
       </x:c>
-      <x:c r="C4" s="66" t="str"/>
-      <x:c r="D4" s="66" t="str">
+      <x:c r="C4" s="77"/>
+      <x:c r="D4" s="77" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E4" s="66" t="str">
+      <x:c r="E4" s="77"/>
+      <x:c r="F4" s="77" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F4" s="66" t="str">
+      <x:c r="G4" s="77"/>
+      <x:c r="H4" s="77" t="str">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G4" s="66" t="str">
+      <x:c r="I4" s="77"/>
+      <x:c r="J4" s="77" t="str">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="H4" s="64" t="str">
+      <x:c r="K4" s="77"/>
+      <x:c r="L4" s="77" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="I4" s="64" t="str">
+      <x:c r="M4" s="78" t="str">
         <x:v>matematicas</x:v>
       </x:c>
-      <x:c r="J4" s="66" t="str">
+      <x:c r="N4" s="78" t="str">
         <x:v>algebra;ecuaciones</x:v>
       </x:c>
-      <x:c r="K4" s="64" t="str">
+      <x:c r="O4" s="78" t="str">
         <x:v>basico</x:v>
       </x:c>
-      <x:c r="L4" s="64" t="str">
+      <x:c r="P4" s="78" t="str">
         <x:v>SI</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="64" t="str">
+    <x:row r="5" ht="32" customHeight="1">
+      <x:c r="A5" s="77" t="str">
         <x:v>MAT-ALG-002</x:v>
       </x:c>
-      <x:c r="B5" s="66" t="str">
+      <x:c r="B5" s="77" t="str">
         <x:v>Simplifica: 2(a + 3) + a.</x:v>
       </x:c>
-      <x:c r="C5" s="66" t="str"/>
-      <x:c r="D5" s="66" t="str">
+      <x:c r="C5" s="77"/>
+      <x:c r="D5" s="77" t="str">
         <x:v>2a + 3</x:v>
       </x:c>
-      <x:c r="E5" s="66" t="str">
+      <x:c r="E5" s="77"/>
+      <x:c r="F5" s="77" t="str">
         <x:v>3a + 3</x:v>
       </x:c>
-      <x:c r="F5" s="66" t="str">
+      <x:c r="G5" s="77"/>
+      <x:c r="H5" s="77" t="str">
         <x:v>3a + 6</x:v>
       </x:c>
-      <x:c r="G5" s="66" t="str">
+      <x:c r="I5" s="77"/>
+      <x:c r="J5" s="77" t="str">
         <x:v>2a + 6</x:v>
       </x:c>
-      <x:c r="H5" s="64" t="str">
+      <x:c r="K5" s="77"/>
+      <x:c r="L5" s="77" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="I5" s="64" t="str">
+      <x:c r="M5" s="78" t="str">
         <x:v>matematicas</x:v>
       </x:c>
-      <x:c r="J5" s="66" t="str">
+      <x:c r="N5" s="78" t="str">
         <x:v>algebra;expresiones</x:v>
       </x:c>
-      <x:c r="K5" s="64" t="str">
+      <x:c r="O5" s="78" t="str">
         <x:v>intermedio</x:v>
       </x:c>
-      <x:c r="L5" s="64" t="str">
+      <x:c r="P5" s="78" t="str">
         <x:v>SI</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="64" t="str">
+    <x:row r="6" ht="32" customHeight="1">
+      <x:c r="A6" s="77" t="str">
         <x:v>MAT-POR-001</x:v>
       </x:c>
-      <x:c r="B6" s="66" t="str">
+      <x:c r="B6" s="77" t="str">
         <x:v>Un artículo cuesta $800 y tiene 25% de descuento. ¿Cuál es su precio final?</x:v>
       </x:c>
-      <x:c r="C6" s="66" t="str"/>
-      <x:c r="D6" s="66" t="str">
+      <x:c r="C6" s="77"/>
+      <x:c r="D6" s="77" t="str">
         <x:v>$200</x:v>
       </x:c>
-      <x:c r="E6" s="66" t="str">
+      <x:c r="E6" s="77"/>
+      <x:c r="F6" s="77" t="str">
         <x:v>$575</x:v>
       </x:c>
-      <x:c r="F6" s="66" t="str">
+      <x:c r="G6" s="77"/>
+      <x:c r="H6" s="77" t="str">
         <x:v>$600</x:v>
       </x:c>
-      <x:c r="G6" s="66" t="str">
+      <x:c r="I6" s="77"/>
+      <x:c r="J6" s="77" t="str">
         <x:v>$625</x:v>
       </x:c>
-      <x:c r="H6" s="64" t="str">
+      <x:c r="K6" s="77"/>
+      <x:c r="L6" s="77" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="I6" s="64" t="str">
+      <x:c r="M6" s="78" t="str">
         <x:v>matematicas</x:v>
       </x:c>
-      <x:c r="J6" s="66" t="str">
+      <x:c r="N6" s="78" t="str">
         <x:v>porcentajes;problemas</x:v>
       </x:c>
-      <x:c r="K6" s="64" t="str">
+      <x:c r="O6" s="78" t="str">
         <x:v>basico</x:v>
       </x:c>
-      <x:c r="L6" s="64" t="str">
+      <x:c r="P6" s="78" t="str">
         <x:v>SI</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="64" t="str">
+    <x:row r="7" ht="32" customHeight="1">
+      <x:c r="A7" s="77" t="str">
         <x:v>MAT-PRO-001</x:v>
       </x:c>
-      <x:c r="B7" s="66" t="str">
+      <x:c r="B7" s="77" t="str">
         <x:v>Una receta para 4 personas usa 300 g de harina. ¿Cuánta harina se necesita para 10 personas?</x:v>
       </x:c>
-      <x:c r="C7" s="66" t="str"/>
-      <x:c r="D7" s="66" t="str">
+      <x:c r="C7" s="77"/>
+      <x:c r="D7" s="77" t="str">
         <x:v>600 g</x:v>
       </x:c>
-      <x:c r="E7" s="66" t="str">
+      <x:c r="E7" s="77"/>
+      <x:c r="F7" s="77" t="str">
         <x:v>700 g</x:v>
       </x:c>
-      <x:c r="F7" s="66" t="str">
+      <x:c r="G7" s="77"/>
+      <x:c r="H7" s="77" t="str">
         <x:v>750 g</x:v>
       </x:c>
-      <x:c r="G7" s="66" t="str">
+      <x:c r="I7" s="77"/>
+      <x:c r="J7" s="77" t="str">
         <x:v>900 g</x:v>
       </x:c>
-      <x:c r="H7" s="64" t="str">
+      <x:c r="K7" s="77"/>
+      <x:c r="L7" s="77" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="I7" s="64" t="str">
+      <x:c r="M7" s="78" t="str">
         <x:v>matematicas</x:v>
       </x:c>
-      <x:c r="J7" s="66" t="str">
+      <x:c r="N7" s="78" t="str">
         <x:v>proporciones;regla-de-tres</x:v>
       </x:c>
-      <x:c r="K7" s="64" t="str">
+      <x:c r="O7" s="78" t="str">
         <x:v>intermedio</x:v>
       </x:c>
-      <x:c r="L7" s="64" t="str">
+      <x:c r="P7" s="78" t="str">
         <x:v>SI</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="64" t="str">
+    <x:row r="8" ht="32" customHeight="1">
+      <x:c r="A8" s="77" t="str">
         <x:v>MAT-GEO-001</x:v>
       </x:c>
-      <x:c r="B8" s="66" t="str">
+      <x:c r="B8" s="77" t="str">
         <x:v>¿Cuál es el área de un rectángulo de 8 cm de largo y 5 cm de ancho?</x:v>
       </x:c>
-      <x:c r="C8" s="66" t="str"/>
-      <x:c r="D8" s="66" t="str">
+      <x:c r="C8" s="77"/>
+      <x:c r="D8" s="77" t="str">
         <x:v>13 cm²</x:v>
       </x:c>
-      <x:c r="E8" s="66" t="str">
+      <x:c r="E8" s="77"/>
+      <x:c r="F8" s="77" t="str">
         <x:v>26 cm²</x:v>
       </x:c>
-      <x:c r="F8" s="66" t="str">
+      <x:c r="G8" s="77"/>
+      <x:c r="H8" s="77" t="str">
         <x:v>40 cm²</x:v>
       </x:c>
-      <x:c r="G8" s="66" t="str">
+      <x:c r="I8" s="77"/>
+      <x:c r="J8" s="77" t="str">
         <x:v>80 cm²</x:v>
       </x:c>
-      <x:c r="H8" s="64" t="str">
+      <x:c r="K8" s="77"/>
+      <x:c r="L8" s="77" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="I8" s="64" t="str">
+      <x:c r="M8" s="78" t="str">
         <x:v>matematicas</x:v>
       </x:c>
-      <x:c r="J8" s="66" t="str">
+      <x:c r="N8" s="78" t="str">
         <x:v>geometria;area</x:v>
       </x:c>
-      <x:c r="K8" s="64" t="str">
+      <x:c r="O8" s="78" t="str">
         <x:v>basico</x:v>
       </x:c>
-      <x:c r="L8" s="64" t="str">
+      <x:c r="P8" s="78" t="str">
         <x:v>SI</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="64" t="str">
+    <x:row r="9" ht="32" customHeight="1">
+      <x:c r="A9" s="77" t="str">
         <x:v>MAT-GEO-002</x:v>
       </x:c>
-      <x:c r="B9" s="66" t="str">
+      <x:c r="B9" s="77" t="str">
         <x:v>Un triángulo tiene base de 10 cm y altura de 6 cm. ¿Cuál es su área?</x:v>
       </x:c>
-      <x:c r="C9" s="66" t="str"/>
-      <x:c r="D9" s="66" t="str">
+      <x:c r="C9" s="77"/>
+      <x:c r="D9" s="77" t="str">
         <x:v>16 cm²</x:v>
       </x:c>
-      <x:c r="E9" s="66" t="str">
+      <x:c r="E9" s="77"/>
+      <x:c r="F9" s="77" t="str">
         <x:v>30 cm²</x:v>
       </x:c>
-      <x:c r="F9" s="66" t="str">
+      <x:c r="G9" s="77"/>
+      <x:c r="H9" s="77" t="str">
         <x:v>60 cm²</x:v>
       </x:c>
-      <x:c r="G9" s="66" t="str">
+      <x:c r="I9" s="77"/>
+      <x:c r="J9" s="77" t="str">
         <x:v>120 cm²</x:v>
       </x:c>
-      <x:c r="H9" s="64" t="str">
+      <x:c r="K9" s="77"/>
+      <x:c r="L9" s="77" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="I9" s="64" t="str">
+      <x:c r="M9" s="78" t="str">
         <x:v>matematicas</x:v>
       </x:c>
-      <x:c r="J9" s="66" t="str">
+      <x:c r="N9" s="78" t="str">
         <x:v>geometria;triangulos</x:v>
       </x:c>
-      <x:c r="K9" s="64" t="str">
+      <x:c r="O9" s="78" t="str">
         <x:v>basico</x:v>
       </x:c>
-      <x:c r="L9" s="64" t="str">
+      <x:c r="P9" s="78" t="str">
         <x:v>SI</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="64" t="str">
+    <x:row r="10" ht="32" customHeight="1">
+      <x:c r="A10" s="77" t="str">
         <x:v>MAT-EST-001</x:v>
       </x:c>
-      <x:c r="B10" s="66" t="str">
+      <x:c r="B10" s="77" t="str">
         <x:v>¿Cuál es la media de 4, 6, 8 y 10?</x:v>
       </x:c>
-      <x:c r="C10" s="66" t="str"/>
-      <x:c r="D10" s="66" t="str">
+      <x:c r="C10" s="77"/>
+      <x:c r="D10" s="77" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="E10" s="66" t="str">
+      <x:c r="E10" s="77"/>
+      <x:c r="F10" s="77" t="str">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F10" s="66" t="str">
+      <x:c r="G10" s="77"/>
+      <x:c r="H10" s="77" t="str">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G10" s="66" t="str">
+      <x:c r="I10" s="77"/>
+      <x:c r="J10" s="77" t="str">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="H10" s="64" t="str">
+      <x:c r="K10" s="77"/>
+      <x:c r="L10" s="77" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="I10" s="64" t="str">
+      <x:c r="M10" s="78" t="str">
         <x:v>matematicas</x:v>
       </x:c>
-      <x:c r="J10" s="66" t="str">
+      <x:c r="N10" s="78" t="str">
         <x:v>estadistica;media</x:v>
       </x:c>
-      <x:c r="K10" s="64" t="str">
+      <x:c r="O10" s="78" t="str">
         <x:v>basico</x:v>
       </x:c>
-      <x:c r="L10" s="64" t="str">
+      <x:c r="P10" s="78" t="str">
         <x:v>SI</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="64" t="str">
+    <x:row r="11" ht="32" customHeight="1">
+      <x:c r="A11" s="77" t="str">
         <x:v>MAT-SEQ-001</x:v>
       </x:c>
-      <x:c r="B11" s="66" t="str">
+      <x:c r="B11" s="77" t="str">
         <x:v>Completa la sucesión: 2, 6, 12, 20, __.</x:v>
       </x:c>
-      <x:c r="C11" s="66" t="str"/>
-      <x:c r="D11" s="66" t="str">
+      <x:c r="C11" s="77"/>
+      <x:c r="D11" s="77" t="str">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E11" s="66" t="str">
+      <x:c r="E11" s="77"/>
+      <x:c r="F11" s="77" t="str">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F11" s="66" t="str">
+      <x:c r="G11" s="77"/>
+      <x:c r="H11" s="77" t="str">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G11" s="66" t="str">
+      <x:c r="I11" s="77"/>
+      <x:c r="J11" s="77" t="str">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="H11" s="64" t="str">
+      <x:c r="K11" s="77"/>
+      <x:c r="L11" s="77" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="I11" s="64" t="str">
+      <x:c r="M11" s="78" t="str">
         <x:v>matematicas</x:v>
       </x:c>
-      <x:c r="J11" s="66" t="str">
+      <x:c r="N11" s="78" t="str">
         <x:v>sucesiones;patrones</x:v>
       </x:c>
-      <x:c r="K11" s="64" t="str">
+      <x:c r="O11" s="78" t="str">
         <x:v>intermedio</x:v>
       </x:c>
-      <x:c r="L11" s="64" t="str">
+      <x:c r="P11" s="78" t="str">
         <x:v>SI</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="64" t="str">
+    <x:row r="12" ht="32" customHeight="1">
+      <x:c r="A12" s="77" t="str">
         <x:v>LEC-INF-001</x:v>
       </x:c>
-      <x:c r="B12" s="66" t="str">
+      <x:c r="B12" s="77" t="str">
         <x:v>Lee: “El parque cerró temprano porque comenzó una tormenta eléctrica”. ¿Cuál fue la causa del cierre?</x:v>
       </x:c>
-      <x:c r="C12" s="66" t="str"/>
-      <x:c r="D12" s="66" t="str">
+      <x:c r="C12" s="77"/>
+      <x:c r="D12" s="77" t="str">
         <x:v>La falta de visitantes</x:v>
       </x:c>
-      <x:c r="E12" s="66" t="str">
+      <x:c r="E12" s="77"/>
+      <x:c r="F12" s="77" t="str">
         <x:v>Una tormenta eléctrica</x:v>
       </x:c>
-      <x:c r="F12" s="66" t="str">
+      <x:c r="G12" s="77"/>
+      <x:c r="H12" s="77" t="str">
         <x:v>El horario de invierno</x:v>
       </x:c>
-      <x:c r="G12" s="66" t="str">
+      <x:c r="I12" s="77"/>
+      <x:c r="J12" s="77" t="str">
         <x:v>Una reparación</x:v>
       </x:c>
-      <x:c r="H12" s="64" t="str">
+      <x:c r="K12" s="77"/>
+      <x:c r="L12" s="77" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="I12" s="64" t="str">
+      <x:c r="M12" s="78" t="str">
         <x:v>comprension-lectora</x:v>
       </x:c>
-      <x:c r="J12" s="66" t="str">
+      <x:c r="N12" s="78" t="str">
         <x:v>causa-efecto;lectura</x:v>
       </x:c>
-      <x:c r="K12" s="64" t="str">
+      <x:c r="O12" s="78" t="str">
         <x:v>basico</x:v>
       </x:c>
-      <x:c r="L12" s="64" t="str">
+      <x:c r="P12" s="78" t="str">
         <x:v>SI</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="64" t="str">
+    <x:row r="13" ht="32" customHeight="1">
+      <x:c r="A13" s="77" t="str">
         <x:v>LEC-VOC-001</x:v>
       </x:c>
-      <x:c r="B13" s="66" t="str">
+      <x:c r="B13" s="77" t="str">
         <x:v>En la oración “La respuesta fue ambigua”, la palabra “ambigua” significa:</x:v>
       </x:c>
-      <x:c r="C13" s="66" t="str"/>
-      <x:c r="D13" s="66" t="str">
+      <x:c r="C13" s="77"/>
+      <x:c r="D13" s="77" t="str">
         <x:v>clara y precisa</x:v>
       </x:c>
-      <x:c r="E13" s="66" t="str">
+      <x:c r="E13" s="77"/>
+      <x:c r="F13" s="77" t="str">
         <x:v>difícil de pronunciar</x:v>
       </x:c>
-      <x:c r="F13" s="66" t="str">
+      <x:c r="G13" s="77"/>
+      <x:c r="H13" s="77" t="str">
         <x:v>que admite más de una interpretación</x:v>
       </x:c>
-      <x:c r="G13" s="66" t="str">
+      <x:c r="I13" s="77"/>
+      <x:c r="J13" s="77" t="str">
         <x:v>completamente falsa</x:v>
       </x:c>
-      <x:c r="H13" s="64" t="str">
+      <x:c r="K13" s="77"/>
+      <x:c r="L13" s="77" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="I13" s="64" t="str">
+      <x:c r="M13" s="78" t="str">
         <x:v>comprension-lectora</x:v>
       </x:c>
-      <x:c r="J13" s="66" t="str">
+      <x:c r="N13" s="78" t="str">
         <x:v>vocabulario;contexto</x:v>
       </x:c>
-      <x:c r="K13" s="64" t="str">
+      <x:c r="O13" s="78" t="str">
         <x:v>intermedio</x:v>
       </x:c>
-      <x:c r="L13" s="64" t="str">
+      <x:c r="P13" s="78" t="str">
         <x:v>SI</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="64" t="str">
+    <x:row r="14" ht="32" customHeight="1">
+      <x:c r="A14" s="77" t="str">
         <x:v>LEC-IDE-001</x:v>
       </x:c>
-      <x:c r="B14" s="66" t="str">
+      <x:c r="B14" s="77" t="str">
         <x:v>Lee: “Dormir lo suficiente mejora la atención, la memoria y el estado de ánimo”. ¿Cuál es la idea principal?</x:v>
       </x:c>
-      <x:c r="C14" s="66" t="str"/>
-      <x:c r="D14" s="66" t="str">
+      <x:c r="C14" s="77"/>
+      <x:c r="D14" s="77" t="str">
         <x:v>La memoria funciona solo de noche</x:v>
       </x:c>
-      <x:c r="E14" s="66" t="str">
+      <x:c r="E14" s="77"/>
+      <x:c r="F14" s="77" t="str">
         <x:v>Dormir bien beneficia varias funciones personales</x:v>
       </x:c>
-      <x:c r="F14" s="66" t="str">
+      <x:c r="G14" s="77"/>
+      <x:c r="H14" s="77" t="str">
         <x:v>El estado de ánimo depende de la alimentación</x:v>
       </x:c>
-      <x:c r="G14" s="66" t="str">
+      <x:c r="I14" s="77"/>
+      <x:c r="J14" s="77" t="str">
         <x:v>La atención no se puede mejorar</x:v>
       </x:c>
-      <x:c r="H14" s="64" t="str">
+      <x:c r="K14" s="77"/>
+      <x:c r="L14" s="77" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="I14" s="64" t="str">
+      <x:c r="M14" s="78" t="str">
         <x:v>comprension-lectora</x:v>
       </x:c>
-      <x:c r="J14" s="66" t="str">
+      <x:c r="N14" s="78" t="str">
         <x:v>idea-principal;lectura</x:v>
       </x:c>
-      <x:c r="K14" s="64" t="str">
+      <x:c r="O14" s="78" t="str">
         <x:v>basico</x:v>
       </x:c>
-      <x:c r="L14" s="64" t="str">
+      <x:c r="P14" s="78" t="str">
         <x:v>SI</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="64" t="str">
+    <x:row r="15" ht="32" customHeight="1">
+      <x:c r="A15" s="77" t="str">
         <x:v>LEC-INF-002</x:v>
       </x:c>
-      <x:c r="B15" s="66" t="str">
+      <x:c r="B15" s="77" t="str">
         <x:v>Lee: “Aunque llevaba paraguas, Elena llegó empapada”. ¿Qué se puede inferir?</x:v>
       </x:c>
-      <x:c r="C15" s="66" t="str"/>
-      <x:c r="D15" s="66" t="str">
+      <x:c r="C15" s="77"/>
+      <x:c r="D15" s="77" t="str">
         <x:v>No llovió</x:v>
       </x:c>
-      <x:c r="E15" s="66" t="str">
+      <x:c r="E15" s="77"/>
+      <x:c r="F15" s="77" t="str">
         <x:v>El paraguas no fue suficiente</x:v>
       </x:c>
-      <x:c r="F15" s="66" t="str">
+      <x:c r="G15" s="77"/>
+      <x:c r="H15" s="77" t="str">
         <x:v>Elena olvidó el paraguas</x:v>
       </x:c>
-      <x:c r="G15" s="66" t="str">
+      <x:c r="I15" s="77"/>
+      <x:c r="J15" s="77" t="str">
         <x:v>Elena llegó en automóvil</x:v>
       </x:c>
-      <x:c r="H15" s="64" t="str">
+      <x:c r="K15" s="77"/>
+      <x:c r="L15" s="77" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="I15" s="64" t="str">
+      <x:c r="M15" s="78" t="str">
         <x:v>comprension-lectora</x:v>
       </x:c>
-      <x:c r="J15" s="66" t="str">
+      <x:c r="N15" s="78" t="str">
         <x:v>inferencia;lectura</x:v>
       </x:c>
-      <x:c r="K15" s="64" t="str">
+      <x:c r="O15" s="78" t="str">
         <x:v>intermedio</x:v>
       </x:c>
-      <x:c r="L15" s="64" t="str">
+      <x:c r="P15" s="78" t="str">
         <x:v>SI</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="64" t="str">
+    <x:row r="16" ht="32" customHeight="1">
+      <x:c r="A16" s="77" t="str">
         <x:v>RED-CON-001</x:v>
       </x:c>
-      <x:c r="B16" s="66" t="str">
+      <x:c r="B16" s="77" t="str">
         <x:v>Elige el conector adecuado: “Estudió durante varias semanas; ____, obtuvo un buen resultado”.</x:v>
       </x:c>
-      <x:c r="C16" s="66" t="str"/>
-      <x:c r="D16" s="66" t="str">
+      <x:c r="C16" s="77"/>
+      <x:c r="D16" s="77" t="str">
         <x:v>sin embargo</x:v>
       </x:c>
-      <x:c r="E16" s="66" t="str">
+      <x:c r="E16" s="77"/>
+      <x:c r="F16" s="77" t="str">
         <x:v>por eso</x:v>
       </x:c>
-      <x:c r="F16" s="66" t="str">
+      <x:c r="G16" s="77"/>
+      <x:c r="H16" s="77" t="str">
         <x:v>aunque</x:v>
       </x:c>
-      <x:c r="G16" s="66" t="str">
+      <x:c r="I16" s="77"/>
+      <x:c r="J16" s="77" t="str">
         <x:v>mientras</x:v>
       </x:c>
-      <x:c r="H16" s="64" t="str">
+      <x:c r="K16" s="77"/>
+      <x:c r="L16" s="77" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="I16" s="64" t="str">
+      <x:c r="M16" s="78" t="str">
         <x:v>redaccion-indirecta</x:v>
       </x:c>
-      <x:c r="J16" s="66" t="str">
+      <x:c r="N16" s="78" t="str">
         <x:v>conectores;coherencia</x:v>
       </x:c>
-      <x:c r="K16" s="64" t="str">
+      <x:c r="O16" s="78" t="str">
         <x:v>basico</x:v>
       </x:c>
-      <x:c r="L16" s="64" t="str">
+      <x:c r="P16" s="78" t="str">
         <x:v>SI</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="64" t="str">
+    <x:row r="17" ht="32" customHeight="1">
+      <x:c r="A17" s="77" t="str">
         <x:v>RED-ORT-001</x:v>
       </x:c>
-      <x:c r="B17" s="66" t="str">
+      <x:c r="B17" s="77" t="str">
         <x:v>¿Cuál oración está escrita correctamente?</x:v>
       </x:c>
-      <x:c r="C17" s="66" t="str"/>
-      <x:c r="D17" s="66" t="str">
+      <x:c r="C17" s="77"/>
+      <x:c r="D17" s="77" t="str">
         <x:v>Aun no se si vendrá.</x:v>
       </x:c>
-      <x:c r="E17" s="66" t="str">
+      <x:c r="E17" s="77"/>
+      <x:c r="F17" s="77" t="str">
         <x:v>Aún no sé si vendrá.</x:v>
       </x:c>
-      <x:c r="F17" s="66" t="str">
+      <x:c r="G17" s="77"/>
+      <x:c r="H17" s="77" t="str">
         <x:v>Aún no se sí vendrá.</x:v>
       </x:c>
-      <x:c r="G17" s="66" t="str">
+      <x:c r="I17" s="77"/>
+      <x:c r="J17" s="77" t="str">
         <x:v>Aun no sé sí vendra.</x:v>
       </x:c>
-      <x:c r="H17" s="64" t="str">
+      <x:c r="K17" s="77"/>
+      <x:c r="L17" s="77" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="I17" s="64" t="str">
+      <x:c r="M17" s="78" t="str">
         <x:v>redaccion-indirecta</x:v>
       </x:c>
-      <x:c r="J17" s="66" t="str">
+      <x:c r="N17" s="78" t="str">
         <x:v>acentuacion;ortografia</x:v>
       </x:c>
-      <x:c r="K17" s="64" t="str">
+      <x:c r="O17" s="78" t="str">
         <x:v>intermedio</x:v>
       </x:c>
-      <x:c r="L17" s="64" t="str">
+      <x:c r="P17" s="78" t="str">
         <x:v>SI</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="64" t="str">
+    <x:row r="18" ht="32" customHeight="1">
+      <x:c r="A18" s="77" t="str">
         <x:v>RED-PUN-001</x:v>
       </x:c>
-      <x:c r="B18" s="66" t="str">
+      <x:c r="B18" s="77" t="str">
         <x:v>Selecciona la opción con puntuación correcta.</x:v>
       </x:c>
-      <x:c r="C18" s="66" t="str"/>
-      <x:c r="D18" s="66" t="str">
+      <x:c r="C18" s="77"/>
+      <x:c r="D18" s="77" t="str">
         <x:v>María compró: pan leche y fruta.</x:v>
       </x:c>
-      <x:c r="E18" s="66" t="str">
+      <x:c r="E18" s="77"/>
+      <x:c r="F18" s="77" t="str">
         <x:v>María compró pan, leche y fruta.</x:v>
       </x:c>
-      <x:c r="F18" s="66" t="str">
+      <x:c r="G18" s="77"/>
+      <x:c r="H18" s="77" t="str">
         <x:v>María, compró pan leche, y fruta.</x:v>
       </x:c>
-      <x:c r="G18" s="66" t="str">
+      <x:c r="I18" s="77"/>
+      <x:c r="J18" s="77" t="str">
         <x:v>María compró pan leche y, fruta.</x:v>
       </x:c>
-      <x:c r="H18" s="64" t="str">
+      <x:c r="K18" s="77"/>
+      <x:c r="L18" s="77" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="I18" s="64" t="str">
+      <x:c r="M18" s="78" t="str">
         <x:v>redaccion-indirecta</x:v>
       </x:c>
-      <x:c r="J18" s="66" t="str">
+      <x:c r="N18" s="78" t="str">
         <x:v>puntuacion;enumeracion</x:v>
       </x:c>
-      <x:c r="K18" s="64" t="str">
+      <x:c r="O18" s="78" t="str">
         <x:v>basico</x:v>
       </x:c>
-      <x:c r="L18" s="64" t="str">
+      <x:c r="P18" s="78" t="str">
         <x:v>SI</x:v>
       </x:c>
     </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="64" t="str">
+    <x:row r="19" ht="32" customHeight="1">
+      <x:c r="A19" s="77" t="str">
         <x:v>RED-COH-001</x:v>
       </x:c>
-      <x:c r="B19" s="66" t="str">
+      <x:c r="B19" s="77" t="str">
         <x:v>¿Qué oración expresa la idea con mayor claridad?</x:v>
       </x:c>
-      <x:c r="C19" s="66" t="str"/>
-      <x:c r="D19" s="66" t="str">
+      <x:c r="C19" s="77"/>
+      <x:c r="D19" s="77" t="str">
         <x:v>Debido a que llovía por eso se canceló.</x:v>
       </x:c>
-      <x:c r="E19" s="66" t="str">
+      <x:c r="E19" s="77"/>
+      <x:c r="F19" s="77" t="str">
         <x:v>Se canceló porque debido a la lluvia.</x:v>
       </x:c>
-      <x:c r="F19" s="66" t="str">
+      <x:c r="G19" s="77"/>
+      <x:c r="H19" s="77" t="str">
         <x:v>La actividad se canceló debido a la lluvia.</x:v>
       </x:c>
-      <x:c r="G19" s="66" t="str">
+      <x:c r="I19" s="77"/>
+      <x:c r="J19" s="77" t="str">
         <x:v>La lluvia debido canceló la actividad.</x:v>
       </x:c>
-      <x:c r="H19" s="64" t="str">
+      <x:c r="K19" s="77"/>
+      <x:c r="L19" s="77" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="I19" s="64" t="str">
+      <x:c r="M19" s="78" t="str">
         <x:v>redaccion-indirecta</x:v>
       </x:c>
-      <x:c r="J19" s="66" t="str">
+      <x:c r="N19" s="78" t="str">
         <x:v>claridad;coherencia</x:v>
       </x:c>
-      <x:c r="K19" s="64" t="str">
+      <x:c r="O19" s="78" t="str">
         <x:v>intermedio</x:v>
       </x:c>
-      <x:c r="L19" s="64" t="str">
+      <x:c r="P19" s="78" t="str">
         <x:v>SI</x:v>
       </x:c>
     </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="64" t="str">
+    <x:row r="20" ht="32" customHeight="1">
+      <x:c r="A20" s="77" t="str">
         <x:v>MAT-RAZ-001</x:v>
       </x:c>
-      <x:c r="B20" s="66" t="str">
+      <x:c r="B20" s="77" t="str">
         <x:v>Si todos los cuadernos son útiles y algunos objetos útiles son reciclados, ¿qué afirmación es necesariamente verdadera?</x:v>
       </x:c>
-      <x:c r="C20" s="66" t="str"/>
-      <x:c r="D20" s="66" t="str">
+      <x:c r="C20" s="77"/>
+      <x:c r="D20" s="77" t="str">
         <x:v>Todos los reciclados son cuadernos</x:v>
       </x:c>
-      <x:c r="E20" s="66" t="str">
+      <x:c r="E20" s="77"/>
+      <x:c r="F20" s="77" t="str">
         <x:v>Todos los cuadernos son reciclados</x:v>
       </x:c>
-      <x:c r="F20" s="66" t="str">
+      <x:c r="G20" s="77"/>
+      <x:c r="H20" s="77" t="str">
         <x:v>Todos los cuadernos son útiles</x:v>
       </x:c>
-      <x:c r="G20" s="66" t="str">
+      <x:c r="I20" s="77"/>
+      <x:c r="J20" s="77" t="str">
         <x:v>Ningún cuaderno es reciclado</x:v>
       </x:c>
-      <x:c r="H20" s="64" t="str">
+      <x:c r="K20" s="77"/>
+      <x:c r="L20" s="77" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="I20" s="64" t="str">
+      <x:c r="M20" s="78" t="str">
         <x:v>matematicas</x:v>
       </x:c>
-      <x:c r="J20" s="66" t="str">
+      <x:c r="N20" s="78" t="str">
         <x:v>razonamiento;logica</x:v>
       </x:c>
-      <x:c r="K20" s="64" t="str">
+      <x:c r="O20" s="78" t="str">
         <x:v>intermedio</x:v>
       </x:c>
-      <x:c r="L20" s="64" t="str">
+      <x:c r="P20" s="78" t="str">
         <x:v>SI</x:v>
       </x:c>
     </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="64" t="str">
+    <x:row r="21" ht="32" customHeight="1">
+      <x:c r="A21" s="77" t="str">
         <x:v>MAT-PROB-001</x:v>
       </x:c>
-      <x:c r="B21" s="66" t="str">
+      <x:c r="B21" s="77" t="str">
         <x:v>En una bolsa hay 3 fichas rojas y 2 azules. ¿Cuál es la probabilidad de sacar una ficha azul?</x:v>
       </x:c>
-      <x:c r="C21" s="66" t="str"/>
-      <x:c r="D21" s="66" t="str">
+      <x:c r="C21" s="77"/>
+      <x:c r="D21" s="77" t="str">
         <x:v>2/3</x:v>
       </x:c>
-      <x:c r="E21" s="66" t="str">
+      <x:c r="E21" s="77"/>
+      <x:c r="F21" s="77" t="str">
         <x:v>2/5</x:v>
       </x:c>
-      <x:c r="F21" s="66" t="str">
+      <x:c r="G21" s="77"/>
+      <x:c r="H21" s="77" t="str">
         <x:v>3/5</x:v>
       </x:c>
-      <x:c r="G21" s="66" t="str">
+      <x:c r="I21" s="77"/>
+      <x:c r="J21" s="77" t="str">
         <x:v>1/2</x:v>
       </x:c>
-      <x:c r="H21" s="64" t="str">
+      <x:c r="K21" s="77"/>
+      <x:c r="L21" s="77" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="I21" s="64" t="str">
+      <x:c r="M21" s="78" t="str">
         <x:v>matematicas</x:v>
       </x:c>
-      <x:c r="J21" s="66" t="str">
+      <x:c r="N21" s="78" t="str">
         <x:v>probabilidad;fracciones</x:v>
       </x:c>
-      <x:c r="K21" s="64" t="str">
+      <x:c r="O21" s="78" t="str">
         <x:v>intermedio</x:v>
       </x:c>
-      <x:c r="L21" s="64" t="str">
+      <x:c r="P21" s="78" t="str">
         <x:v>SI</x:v>
       </x:c>
     </x:row>
@@ -29395,7 +29433,7 @@
       <x:c r="L2000" s="64"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="3">
+  <x:dataValidations count="6">
     <x:dataValidation type="list" sqref="H2:H2000">
       <x:formula1>Listas!$A$2:$A$5</x:formula1>
     </x:dataValidation>
@@ -29405,10 +29443,19 @@
     <x:dataValidation type="list" sqref="L2:L2000">
       <x:formula1>Listas!$D$2:$D$3</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="L2:L21">
+      <x:formula1>Listas!$A$2:$A$5</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="O2:O21">
+      <x:formula1>Listas!$B$2:$B$4</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="P2:P21">
+      <x:formula1>Listas!$D$2:$D$3</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R986c5a4478644c34"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3354b886f824605"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -39470,7 +39517,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reec1ff81a639475e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc85f0f79ab8f4cd3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -57630,7 +57677,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4cc44e7a9374adb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb5210d0957a49dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -61224,7 +61271,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8b87ef7a09a4af4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77fdef016ac3491e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -61250,7 +61297,7 @@
         <x:v>content_version</x:v>
       </x:c>
       <x:c r="B2" s="64" t="str">
-        <x:v>2026_07_004</x:v>
+        <x:v>2026_07_005</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -61258,7 +61305,7 @@
         <x:v>questions_version</x:v>
       </x:c>
       <x:c r="B3" s="64" t="str">
-        <x:v>questions_001</x:v>
+        <x:v>questions_002</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -61290,7 +61337,7 @@
         <x:v>min_app_version</x:v>
       </x:c>
       <x:c r="B7" s="64" t="str">
-        <x:v>1</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -61670,7 +61717,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34d5e4a96ddc4391"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0f5d1b36b764387"/>
   </x:tableParts>
 </x:worksheet>
 </file>